--- a/artfynd/A 19255-2023 artfynd.xlsx
+++ b/artfynd/A 19255-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430346</v>
       </c>
       <c r="B2" t="n">
-        <v>108704</v>
+        <v>108717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19255-2023 artfynd.xlsx
+++ b/artfynd/A 19255-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430346</v>
       </c>
       <c r="B2" t="n">
-        <v>108717</v>
+        <v>108718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19255-2023 artfynd.xlsx
+++ b/artfynd/A 19255-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430346</v>
       </c>
       <c r="B2" t="n">
-        <v>108718</v>
+        <v>108721</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Veronica Lindström</t>
+          <t>Veronica Lindström, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 19255-2023 artfynd.xlsx
+++ b/artfynd/A 19255-2023 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Veronica Lindström, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Veronica Lindström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 19255-2023 artfynd.xlsx
+++ b/artfynd/A 19255-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430346</v>
       </c>
       <c r="B2" t="n">
-        <v>108721</v>
+        <v>108727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19255-2023 artfynd.xlsx
+++ b/artfynd/A 19255-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430346</v>
       </c>
       <c r="B2" t="n">
-        <v>108727</v>
+        <v>108728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
